--- a/results/Int All Data -0.8/Rando_4_permute.xlsx
+++ b/results/Int All Data -0.8/Rando_4_permute.xlsx
@@ -440,237 +440,237 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7917472202025466</v>
+        <v>0.7914677344563197</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7917472202025466</v>
+        <v>0.7905278848322596</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7912220461718857</v>
+        <v>0.7887833754313116</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7892994434100904</v>
+        <v>0.7882244039388577</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7882582014006509</v>
+        <v>0.7863785021525306</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7881477029633894</v>
+        <v>0.7878773232690446</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7878344197553694</v>
+        <v>0.7872169593912114</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7845326003662034</v>
+        <v>0.7866579878987575</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.782339617910063</v>
+        <v>0.7884791982751737</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7817039454421408</v>
+        <v>0.7874626476756452</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7864954798959388</v>
+        <v>0.7848302982161945</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7866644672049043</v>
+        <v>0.7848302982161945</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7870115478747175</v>
+        <v>0.7849316906015738</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7877824101898121</v>
+        <v>0.7833990720232666</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7945394509190808</v>
+        <v>0.7833652745614735</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8009741023884474</v>
+        <v>0.7822135341147727</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8006608191804273</v>
+        <v>0.7816207651605257</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7894437393091449</v>
+        <v>0.7816207651605257</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7891395621530068</v>
+        <v>0.7853463661949731</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7888600764067799</v>
+        <v>0.7823058204482699</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7911453451964175</v>
+        <v>0.783211872610537</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7862926951251802</v>
+        <v>0.7858871255836629</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7875458279572604</v>
+        <v>0.7843883044671489</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.784480590800646</v>
+        <v>0.7904667692148202</v>
       </c>
     </row>
     <row r="26">
@@ -680,1153 +680,1153 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7924387547964378</v>
+        <v>0.7870609306945396</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.796096760907299</v>
+        <v>0.7877979955478411</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7983118080276151</v>
+        <v>0.7866124576393472</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7983118080276151</v>
+        <v>0.7756228539487343</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8130361188045575</v>
+        <v>0.7762156229029813</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8149834129762641</v>
+        <v>0.7771892699888345</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8106065541158654</v>
+        <v>0.7863693961006485</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8022557791908502</v>
+        <v>0.7847015876751688</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7995805262177242</v>
+        <v>0.7837617380511088</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7967453919875149</v>
+        <v>0.7837617380511088</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7859000841959566</v>
+        <v>0.7842531146199765</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7928534303898371</v>
+        <v>0.7842531146199765</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.792835218286073</v>
+        <v>0.7854724499902636</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7922424493318259</v>
+        <v>0.7903159940096187</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.792555732539846</v>
+        <v>0.7902483990860325</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7929119192615413</v>
+        <v>0.7880554166298922</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7955624808247561</v>
+        <v>0.7911882487100927</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7880254717285108</v>
+        <v>0.7846248866997007</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7873833199544418</v>
+        <v>0.7864031935624416</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.7889835334563351</v>
+        <v>0.7864031935624416</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.7891278293553896</v>
+        <v>0.7911947280162396</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.7833691271218852</v>
+        <v>0.7941923702492677</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.7676373717972965</v>
+        <v>0.7901781774167111</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.7613781869430423</v>
+        <v>0.7924725522582308</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.75114123346376</v>
+        <v>0.793412401882291</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.753183440714699</v>
+        <v>0.789269498508709</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.7556221114552732</v>
+        <v>0.7917510727629582</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.7467461624995972</v>
+        <v>0.7957418000002802</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.7461195960835572</v>
+        <v>0.7841009384837163</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.7434170249547849</v>
+        <v>0.7814165794587082</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.7346450951302236</v>
+        <v>0.780756215580875</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.7346450951302236</v>
+        <v>0.780442932372855</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.731552539817963</v>
+        <v>0.7538840813604721</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.7541518343090818</v>
+        <v>0.7541973645684923</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.7562096269180497</v>
+        <v>0.7567712251562388</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.7583259083987218</v>
+        <v>0.7289033791858068</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.7594009478699544</v>
+        <v>0.7254754760013504</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.7659123003147892</v>
+        <v>0.728921591289571</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.764659167482709</v>
+        <v>0.7326471923240185</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.7700369915846071</v>
+        <v>0.7176433958008492</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7694104251685669</v>
+        <v>0.7267962037570169</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.7739068885181092</v>
+        <v>0.7238479443438109</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7739406859799023</v>
+        <v>0.7431181012901173</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.7731360262030145</v>
+        <v>0.7429738053910628</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.7648801643572318</v>
+        <v>0.7429738053910628</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.7456373255665716</v>
+        <v>0.7342018755665015</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.7600392470836118</v>
+        <v>0.7370214244386819</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.7603525302916319</v>
+        <v>0.7280376037914799</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.7561667234043745</v>
+        <v>0.7451303636396749</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.7536851491501252</v>
+        <v>0.7428021913363622</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.7355574514822552</v>
+        <v>0.726919660806572</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.7355574514822552</v>
+        <v>0.7270210531919514</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.7341223727289157</v>
+        <v>0.7324573661655536</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.7234225866510883</v>
+        <v>0.7328329908056894</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.723475822031322</v>
+        <v>0.7140048276084285</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.7313781239011448</v>
+        <v>0.7137253418622016</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.7306319529959611</v>
+        <v>0.7042501446461318</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.7241114944992442</v>
+        <v>0.7033102950220717</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.6901299853882891</v>
+        <v>0.7043359516734822</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.6810538784075897</v>
+        <v>0.7046154374197091</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.6812657692302304</v>
+        <v>0.7091248593815449</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.7078533393293183</v>
+        <v>0.7062988312032177</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.7054510927962725</v>
+        <v>0.7029294168904654</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.69907493019861</v>
+        <v>0.6997445752447076</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.6964919635589812</v>
+        <v>0.7003711416607478</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.7065014408575939</v>
+        <v>0.6955951925649786</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.7073307920443928</v>
+        <v>0.6927248599419173</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.7029786245939051</v>
+        <v>0.6948775656301178</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.7029786245939051</v>
+        <v>0.6750640225493864</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.7122731017033921</v>
+        <v>0.6628303920785754</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.7122731017033921</v>
+        <v>0.6519941903388993</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.7122731017033921</v>
+        <v>0.5744741955503627</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.730378559590704</v>
+        <v>0.5773704453980115</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.7306580453369309</v>
+        <v>0.5656866803677725</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.7253894938576178</v>
+        <v>0.5676768780531541</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.717981195302398</v>
+        <v>0.574436545528158</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.7126891782278502</v>
+        <v>0.577409496351275</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.7055109825990353</v>
+        <v>0.5851466634725438</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.6809293706597405</v>
+        <v>0.6076016620646081</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.6507527903044363</v>
+        <v>0.5922845823334187</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.6591685334073025</v>
+        <v>0.6017753649075175</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.5567939202393911</v>
+        <v>0.6033755784094109</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.5514927971129613</v>
+        <v>0.5965691548603201</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.5591194657969687</v>
+        <v>0.5760705564918445</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.549613097864841</v>
+        <v>0.5814639659517715</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.549299814656821</v>
+        <v>0.5526860401422786</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.5476202734337241</v>
+        <v>0.5511690069220003</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.5439440552190986</v>
+        <v>0.5511690069220003</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.545240091564854</v>
+        <v>0.5348262705394005</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5429548227752165</v>
+        <v>0.5422021725638859</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5293614135954756</v>
+        <v>0.5261168572633372</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5298618962162253</v>
+        <v>0.5185304653472698</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5308355433020786</v>
+        <v>0.5219856866873724</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.5300399895770729</v>
+        <v>0.5232908290850099</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5294472206228259</v>
+        <v>0.5048682354292663</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5314309390020607</v>
+        <v>0.5070612178854067</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.5281849817388636</v>
+        <v>0.5070612178854067</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.5347691825987552</v>
+        <v>0.5070612178854067</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5317559550076981</v>
+        <v>0.5012869302938733</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5339151400020454</v>
+        <v>0.5019134967099134</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5182536063467781</v>
+        <v>0.5009736470858532</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5168990811293185</v>
+        <v>0.5009736470858532</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.514359018003365</v>
+        <v>0.5006603638778332</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5003470806698131</v>
+        <v>0.5006603638778332</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5000675949235862</v>
+        <v>0.4997205142537731</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5000675949235862</v>
+        <v>0.4991615427613192</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.4997881091773593</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.4997881091773593</v>
+        <v>0.4997205142537731</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.502988536181146</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5048682354292663</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5036151025971861</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.5002703796943448</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.5002703796943448</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.50031328320802</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.50031328320802</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -1836,7 +1836,7 @@
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -1846,7 +1846,7 @@
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -1856,7 +1856,7 @@
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -1866,7 +1866,7 @@
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -1876,7 +1876,7 @@
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -1886,7 +1886,7 @@
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -1896,7 +1896,7 @@
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -1906,7 +1906,7 @@
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -1916,7 +1916,7 @@
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -1926,7 +1926,7 @@
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -1936,7 +1936,7 @@
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -1946,7 +1946,7 @@
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -1956,7 +1956,7 @@
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -1966,7 +1966,7 @@
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -1976,7 +1976,7 @@
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B156" t="n">
